--- a/outputs/evaluation/architecture/design/v2/CF_M08/run_3/CF_M08_arch_eval.xlsx
+++ b/outputs/evaluation/architecture/design/v2/CF_M08/run_3/CF_M08_arch_eval.xlsx
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -440,6 +440,11 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
+          <t>f1</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
           <t>mean semantic meaning</t>
         </is>
       </c>
@@ -456,7 +461,10 @@
       <c r="C2" t="n">
         <v>0.4194</v>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D2" t="n">
+        <v>0.5778</v>
+      </c>
+      <c r="E2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -475,6 +483,9 @@
         <v>0.4138</v>
       </c>
       <c r="D3" t="n">
+        <v>0.5854</v>
+      </c>
+      <c r="E3" t="n">
         <v>0.9759</v>
       </c>
     </row>
@@ -491,6 +502,9 @@
         <v>0.5</v>
       </c>
       <c r="D4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E4" t="n">
         <v>0.7698</v>
       </c>
     </row>
@@ -1199,7 +1213,6 @@
       <c r="D2" t="n">
         <v>0.7698</v>
       </c>
-      <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
           <t>Connector</t>
@@ -1220,7 +1233,6 @@
           <t>['AU_02', 'AU_03']</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
           <t>AU_10</t>
@@ -1231,7 +1243,6 @@
           <t>system service, data service</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
           <t>Connector</t>
@@ -1250,7 +1261,6 @@
           <t>CF_M08_AU04, CF_M08_AU08</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr"/>
       <c r="S2" t="inlineStr">
         <is>
           <t>CF_M08_AU24</t>
@@ -1301,7 +1311,6 @@
           <t>66</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
           <t>Design Pattern</t>
@@ -1312,7 +1321,6 @@
           <t>P_03</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
           <t>Observer</t>
@@ -1331,14 +1339,11 @@
       <c r="P3" t="n">
         <v>66</v>
       </c>
-      <c r="Q3" t="inlineStr"/>
-      <c r="R3" t="inlineStr"/>
       <c r="S3" t="inlineStr">
         <is>
           <t>CF_M08_P04</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1379,7 +1384,6 @@
           <t>67</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
           <t>Design Pattern</t>
@@ -1390,7 +1394,6 @@
           <t>P_04</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
           <t>Singleton</t>
@@ -1409,14 +1412,11 @@
       <c r="P4" t="n">
         <v>67</v>
       </c>
-      <c r="Q4" t="inlineStr"/>
-      <c r="R4" t="inlineStr"/>
       <c r="S4" t="inlineStr">
         <is>
           <t>CF_M08_P05</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1457,7 +1457,6 @@
           <t>66</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
           <t>Design Pattern</t>
@@ -1468,7 +1467,6 @@
           <t>P_02</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
           <t>Component-based</t>
@@ -1487,14 +1485,11 @@
       <c r="P5" t="n">
         <v>66</v>
       </c>
-      <c r="Q5" t="inlineStr"/>
-      <c r="R5" t="inlineStr"/>
       <c r="S5" t="inlineStr">
         <is>
           <t>CF_M08_P03</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1535,14 +1530,11 @@
           <t>41</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr">
         <is>
           <t>AU_01</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
           <t>Security Service</t>
@@ -1566,13 +1558,11 @@
           <t>CF_M08_P01</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr"/>
       <c r="S6" t="inlineStr">
         <is>
           <t>CF_M08_AU02</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1613,14 +1603,11 @@
           <t>42</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr">
         <is>
           <t>AU_03</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
           <t>Data Service</t>
@@ -1644,13 +1631,11 @@
           <t>CF_M08_P01</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr"/>
       <c r="S7" t="inlineStr">
         <is>
           <t>CF_M08_AU07</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1691,14 +1676,11 @@
           <t>41</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr">
         <is>
           <t>AU_08</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
           <t>Docker</t>
@@ -1722,13 +1704,11 @@
           <t>CF_M08_P01</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr"/>
       <c r="S8" t="inlineStr">
         <is>
           <t>CF_M08_AU22</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1774,13 +1754,11 @@
           <t>['AU_03']</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr">
         <is>
           <t>AU_06</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
           <t>PostgreSQL</t>
@@ -1804,13 +1782,11 @@
           <t>CF_M08_AU07</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr"/>
       <c r="S9" t="inlineStr">
         <is>
           <t>CF_M08_AU08</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1851,7 +1827,6 @@
           <t>41</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
           <t>Architectural Pattern</t>
@@ -1862,7 +1837,6 @@
           <t>P_01</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
           <t>Microservices</t>
@@ -1881,14 +1855,11 @@
       <c r="P10" t="n">
         <v>41</v>
       </c>
-      <c r="Q10" t="inlineStr"/>
-      <c r="R10" t="inlineStr"/>
       <c r="S10" t="inlineStr">
         <is>
           <t>CF_M08_P01</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1929,14 +1900,11 @@
           <t>42</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr">
         <is>
           <t>AU_02</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
           <t>System Service</t>
@@ -1960,13 +1928,11 @@
           <t>CF_M08_P01</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr"/>
       <c r="S11" t="inlineStr">
         <is>
           <t>CF_M08_AU04</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2012,13 +1978,11 @@
           <t>['AU_01']</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr">
         <is>
           <t>AU_04</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
           <t>Traefik</t>
@@ -2042,13 +2006,11 @@
           <t>CF_M08_AU02</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr"/>
       <c r="S12" t="inlineStr">
         <is>
           <t>CF_M08_AU03</t>
         </is>
       </c>
-      <c r="T12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2094,13 +2056,11 @@
           <t>['AU_02']</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr">
         <is>
           <t>AU_05</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
           <t>Next.js</t>
@@ -2124,13 +2084,11 @@
           <t>CF_M08_AU04</t>
         </is>
       </c>
-      <c r="R13" t="inlineStr"/>
       <c r="S13" t="inlineStr">
         <is>
           <t>CF_M08_AU05</t>
         </is>
       </c>
-      <c r="T13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2176,13 +2134,11 @@
           <t>['AU_02']</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr">
         <is>
           <t>AU_07</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
           <t>Prisma</t>
@@ -2206,13 +2162,11 @@
           <t>CF_M08_P02</t>
         </is>
       </c>
-      <c r="R14" t="inlineStr"/>
       <c r="S14" t="inlineStr">
         <is>
           <t>CF_M08_AU09</t>
         </is>
       </c>
-      <c r="T14" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2281,7 +2235,6 @@
           <t>Connector</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
           <t>security service, system service</t>
@@ -2378,7 +2331,6 @@
           <t>Amazon EC2</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
           <t>These services run on Amazon EC2 instances</t>
@@ -2414,7 +2366,6 @@
           <t>React</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
           <t>It serves the web application using React</t>
@@ -2445,7 +2396,6 @@
           <t>Connector</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
           <t>system service, authentication, cloud storage, payment processing, analytics, error monitoring, email</t>
@@ -2486,7 +2436,6 @@
           <t>Authentication</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
           <t>Authentication: Use Google for user authentication.</t>
@@ -2522,7 +2471,6 @@
           <t>Google</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
           <t>Authentication: Use Google for user authentication.</t>
@@ -2558,7 +2506,6 @@
           <t>Cloud storage</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
           <t>Cloud storage: Use Amazon S3 to store and retrieve files.</t>
@@ -2594,7 +2541,6 @@
           <t>Amazon S3</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
           <t>Cloud storage: Use Amazon S3 to store and retrieve files.</t>
@@ -2630,7 +2576,6 @@
           <t>Payment processing</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
           <t>Payment processing: Integrates with Stripe to manage payments and subscriptions tions.</t>
@@ -2666,7 +2611,6 @@
           <t>Stripe</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
           <t>Payment processing: Integrates with Stripe to manage payments and subscriptions tions.</t>
@@ -2702,7 +2646,6 @@
           <t>Analytics</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
           <t>Analytics: Implement Google Analytics to track and analyze the traffic of the site.</t>
@@ -2738,7 +2681,6 @@
           <t>Google Analytics</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
           <t>Implement Google Analytics to track and analyze site traffic</t>
@@ -2774,7 +2716,6 @@
           <t>Error monitoring</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
           <t>Error monitoring: Use Sentry to track and manage errors in the application.</t>
@@ -2810,7 +2751,6 @@
           <t>Sentry</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
           <t>Error monitoring: Use Sentry to track and manage errors in the application.</t>
@@ -2846,7 +2786,6 @@
           <t>Email</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
           <t>Connects to Brevo to create, send and schedule emails electronics.</t>
@@ -2882,7 +2821,6 @@
           <t>Brevo</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
           <t>Connects to Brevo to create, send and schedule emails.</t>
@@ -2918,7 +2856,6 @@
           <t>HTTPS</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
           <t>HTTPS, which is the standard for secure communications on the web</t>
@@ -2929,7 +2866,6 @@
           <t>AU_09</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr"/>
       <c r="H17" t="n">
         <v>0.7762</v>
       </c>
@@ -2950,7 +2886,6 @@
           <t>ORM</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
           <t>(footnote) It is a programming technique to convert data between the type system used in an object-oriented programming language and the use of a relational database as a persistence engine (Atencio 2016).</t>
@@ -2986,7 +2921,6 @@
           <t>Client-Server</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
           <t xml:space="preserve"> The Revivack application mainly uses Next.js for system development, which allows to separate the components between client and server rendering</t>
